--- a/sheets/조재수대금교본/검수/옥수수밭 옆에 당신을 묻고.xlsx
+++ b/sheets/조재수대금교본/검수/옥수수밭 옆에 당신을 묻고.xlsx
@@ -3787,7 +3787,7 @@
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌ㅅ</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="C4" s="23"/>
@@ -3858,47 +3858,19 @@
         </is>
       </c>
       <c r="C6" s="24"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="24"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="24"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="24"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J6" s="21"/>
       <c r="K6" s="24"/>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L6" s="21"/>
       <c r="M6" s="24"/>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N6" s="21"/>
       <c r="O6" s="24"/>
-      <c r="P6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P6" s="21"/>
       <c r="Q6" s="24"/>
     </row>
     <row r="7" ht="68.7" customHeight="true">
@@ -3995,11 +3967,7 @@
         </is>
       </c>
       <c r="O8" s="23"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="23"/>
     </row>
     <row r="9" ht="68.7" customHeight="true">
@@ -4032,46 +4000,21 @@
       <c r="C10" s="24"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="E10" s="24"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="24"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="24"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="24"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="24"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N10" s="21"/>
       <c r="O10" s="24"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P10" s="21"/>
       <c r="Q10" s="24"/>
     </row>
     <row r="11" ht="68.7" customHeight="true">
@@ -4200,47 +4143,19 @@
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P14" s="21"/>
       <c r="Q14" s="24"/>
     </row>
     <row r="15" ht="68.7" customHeight="true">
@@ -4372,29 +4287,19 @@
       <c r="C18" s="24"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="E18" s="24"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="G18" s="24"/>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H18" s="21"/>
       <c r="I18" s="24"/>
-      <c r="J18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J18" s="21"/>
       <c r="K18" s="24"/>
       <c r="L18" s="21" t="inlineStr">
         <is>
@@ -4408,11 +4313,7 @@
         </is>
       </c>
       <c r="O18" s="24"/>
-      <c r="P18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P18" s="21"/>
       <c r="Q18" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/옥수수밭 옆에 당신을 묻고.xlsx
+++ b/sheets/조재수대금교본/검수/옥수수밭 옆에 당신을 묻고.xlsx
@@ -3787,7 +3787,7 @@
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌ㅅ</t>
         </is>
       </c>
       <c r="C4" s="23"/>
@@ -3967,7 +3967,11 @@
         </is>
       </c>
       <c r="O8" s="23"/>
-      <c r="P8" s="21"/>
+      <c r="P8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q8" s="23"/>
     </row>
     <row r="9" ht="68.7" customHeight="true">

--- a/sheets/조재수대금교본/검수/옥수수밭 옆에 당신을 묻고.xlsx
+++ b/sheets/조재수대금교본/검수/옥수수밭 옆에 당신을 묻고.xlsx
@@ -3681,28 +3681,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="61.54" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="68.7" customHeight="true">
+    <row r="3" ht="72.04" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="68.7" customHeight="true">
+    <row r="4" ht="72.04" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       <c r="P4" s="21"/>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="68.7" customHeight="true">
+    <row r="5" ht="72.04" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -3849,7 +3849,7 @@
       <c r="P5" s="21"/>
       <c r="Q5" s="23"/>
     </row>
-    <row r="6" ht="68.7" customHeight="true">
+    <row r="6" ht="72.04" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       <c r="P6" s="21"/>
       <c r="Q6" s="24"/>
     </row>
-    <row r="7" ht="68.7" customHeight="true">
+    <row r="7" ht="72.04" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22"/>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="Q7" s="22"/>
     </row>
-    <row r="8" ht="68.7" customHeight="true">
+    <row r="8" ht="72.04" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="Q8" s="23"/>
     </row>
-    <row r="9" ht="68.7" customHeight="true">
+    <row r="9" ht="72.04" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -3998,7 +3998,7 @@
       <c r="P9" s="21"/>
       <c r="Q9" s="23"/>
     </row>
-    <row r="10" ht="68.7" customHeight="true">
+    <row r="10" ht="72.04" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
@@ -4021,7 +4021,7 @@
       <c r="P10" s="21"/>
       <c r="Q10" s="24"/>
     </row>
-    <row r="11" ht="68.7" customHeight="true">
+    <row r="11" ht="72.04" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -4075,7 +4075,7 @@
       </c>
       <c r="Q11" s="22"/>
     </row>
-    <row r="12" ht="68.7" customHeight="true">
+    <row r="12" ht="72.04" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="Q12" s="23"/>
     </row>
-    <row r="13" ht="68.7" customHeight="true">
+    <row r="13" ht="72.04" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4143,7 +4143,7 @@
       <c r="P13" s="21"/>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="68.7" customHeight="true">
+    <row r="14" ht="72.04" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -4162,7 +4162,7 @@
       <c r="P14" s="21"/>
       <c r="Q14" s="24"/>
     </row>
-    <row r="15" ht="68.7" customHeight="true">
+    <row r="15" ht="72.04" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="Q15" s="22"/>
     </row>
-    <row r="16" ht="68.7" customHeight="true">
+    <row r="16" ht="72.04" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="Q16" s="23"/>
     </row>
-    <row r="17" ht="68.7" customHeight="true">
+    <row r="17" ht="72.04" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -4285,7 +4285,7 @@
       <c r="P17" s="21"/>
       <c r="Q17" s="23"/>
     </row>
-    <row r="18" ht="68.7" customHeight="true">
+    <row r="18" ht="72.04" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="24"/>
@@ -4326,6 +4326,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="65"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>